--- a/fhir/ig/cl-urgencia/0.2.0/ValueSet-vs-diagnostico-urgencia.xlsx
+++ b/fhir/ig/cl-urgencia/0.2.0/ValueSet-vs-diagnostico-urgencia.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia/ValueSet/vs-diagnostico-urgencia</t>
+    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/ValueSet/vs-diagnostico-urgencia</t>
   </si>
   <si>
     <t>Version</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T16:36:45-03:00</t>
+    <t>2026-09-24T11:47:41-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/ig/cl-urgencia/0.2.0/ValueSet-vs-diagnostico-urgencia.xlsx
+++ b/fhir/ig/cl-urgencia/0.2.0/ValueSet-vs-diagnostico-urgencia.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:47:41-03:00</t>
+    <t>2026-10-08T00:02:21-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
